--- a/Dokumen Perancangan/Analisa Step Terhadap RPM Maksimal.xlsx
+++ b/Dokumen Perancangan/Analisa Step Terhadap RPM Maksimal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Udin\Kuliah\7. TUGAS AKHIR\Arm Manipulator\Dokumen Perancangan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859136A9-AA0A-4236-BBD6-455F744B5AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C8C102-5A58-4557-845F-1B74D2F8BDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{C1BE2431-0FDA-473A-BABB-CE4E29D4E3DE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C1BE2431-0FDA-473A-BABB-CE4E29D4E3DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>Step</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>30V</t>
+  </si>
+  <si>
+    <t>f (kHz)</t>
   </si>
 </sst>
 </file>
@@ -141,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -157,6 +160,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6204B5B5-B499-406F-8E27-A3D2F299A2FA}">
-  <dimension ref="B1:F15"/>
+  <dimension ref="B1:G15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17" customWidth="1"/>
@@ -480,7 +489,7 @@
     <col min="6" max="6" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:7" ht="18" x14ac:dyDescent="0.3">
       <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
@@ -488,7 +497,7 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -502,10 +511,13 @@
         <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="2">
         <v>200</v>
       </c>
@@ -520,30 +532,38 @@
       <c r="E3" s="2">
         <v>1000</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="2">
+        <f>1/E3*1000</f>
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="2">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="7">
         <v>800</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="7">
         <f>E4*B4/1000000</f>
         <v>0.14399999999999999</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="7">
         <f>1/C4*60</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="7">
         <v>180</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7">
+        <f>1/E4*1000</f>
+        <v>5.5555555555555554</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1600</v>
       </c>
@@ -558,11 +578,15 @@
       <c r="E5" s="2">
         <v>90</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="6">
+        <f>1/E5*1000</f>
+        <v>11.111111111111111</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>3200</v>
       </c>
@@ -570,15 +594,22 @@
         <f>E6*B6/1000000</f>
         <v>0.16</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2">
+        <f>1/C6*60</f>
+        <v>375</v>
+      </c>
       <c r="E6" s="2">
         <v>50</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="2">
+        <f>1/E6*1000</f>
+        <v>20</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>6400</v>
       </c>
@@ -586,8 +617,9 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-    </row>
-    <row r="9" spans="2:6" ht="18" x14ac:dyDescent="0.3">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="9" spans="2:7" ht="18" x14ac:dyDescent="0.3">
       <c r="B9" s="5" t="s">
         <v>4</v>
       </c>
@@ -595,7 +627,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>0</v>
       </c>
@@ -609,7 +641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>200</v>
       </c>
@@ -617,7 +649,7 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>800</v>
       </c>
@@ -625,7 +657,7 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>1600</v>
       </c>
@@ -633,7 +665,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>3200</v>
       </c>
@@ -641,7 +673,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>6400</v>
       </c>
